--- a/docs/downloads/经营分_津河省区__津北片区_2026-10-18.xlsx
+++ b/docs/downloads/经营分_津河省区__津北片区_2026-10-18.xlsx
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
         <v>30</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="T2" t="n">
         <v>20</v>
@@ -1042,14 +1042,14 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         <v>30</v>
       </c>
       <c r="O6" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P6" t="n">
         <v>30</v>
@@ -1291,17 +1291,17 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>7081318591441668127</t>
+          <t>6601273342836082702</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>麗枫酒店· 天津站意式风情区天津之眼店</t>
+          <t>维也纳酒店（天津武清大华总部店）</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>麗枫酒店(天津火车站意大利风情街店)</t>
+          <t>维也纳酒店(天津武清大华总部店)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1313,7 +1313,7 @@
         <v>87</v>
       </c>
       <c r="I9" t="n">
-        <v>3</v>
+        <v>-5</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1333,13 +1333,13 @@
         <v>30</v>
       </c>
       <c r="O9" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P9" t="n">
         <v>30</v>
       </c>
       <c r="Q9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="R9" t="n">
         <v>30</v>
@@ -1379,17 +1379,17 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>6601256643759966222</t>
+          <t>7081318591441668127</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>麗枫酒店·天津武清高铁站大光明中心店</t>
+          <t>麗枫酒店· 天津站意式风情区天津之眼店</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>麗枫酒店(天津武清高铁站大光明中心店)</t>
+          <t>麗枫酒店(天津火车站意大利风情街店)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1401,7 +1401,7 @@
         <v>87</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1467,17 +1467,17 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>7278641233155590185</t>
+          <t>6601256643759966222</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>维也纳智好天津北辰西堤头店</t>
+          <t>麗枫酒店·天津武清高铁站大光明中心店</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>维也纳酒店(天津北辰西堤头店)</t>
+          <t>麗枫酒店(天津武清高铁站大光明中心店)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1486,18 +1486,18 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I11" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>搭门店,稳房源,提质量,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L11" t="n">
         <v>10</v>
@@ -1515,7 +1515,7 @@
         <v>30</v>
       </c>
       <c r="Q11" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R11" t="n">
         <v>30</v>
@@ -1548,40 +1548,44 @@
           <t>津北片区</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>天津市</t>
+        </is>
+      </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>6924421482093234189</t>
+          <t>7278641233155590185</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>希岸Deluxe酒店天津武清友谊百货店</t>
+          <t>维也纳智好天津北辰西堤头店</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>希岸Deluxe酒店(天津武清友谊百货店)</t>
+          <t>维也纳酒店(天津北辰西堤头店)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>搭门店,稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L12" t="n">
         <v>10</v>
@@ -1593,13 +1597,13 @@
         <v>30</v>
       </c>
       <c r="O12" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P12" t="n">
         <v>30</v>
       </c>
       <c r="Q12" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R12" t="n">
         <v>30</v>
@@ -1632,40 +1636,36 @@
           <t>津北片区</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>天津市</t>
-        </is>
-      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>6601273342836082702</t>
+          <t>6924421482093234189</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>维也纳酒店（天津武清大华总部店）</t>
+          <t>希岸Deluxe酒店天津武清友谊百货店</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>维也纳酒店(天津武清大华总部店)</t>
+          <t>希岸Deluxe酒店(天津武清友谊百货店)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H13" t="n">
         <v>92</v>
       </c>
       <c r="I13" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1681,13 +1681,13 @@
         <v>30</v>
       </c>
       <c r="O13" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P13" t="n">
         <v>30</v>
       </c>
       <c r="Q13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="R13" t="n">
         <v>30</v>
@@ -2167,17 +2167,17 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>7487536797837166592</t>
+          <t>6684817408277891079</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>7天优品酒店（天津北辰双街工业园区柴楼地铁站店）</t>
+          <t>维也纳3好酒店（天津北辰双街柴楼地铁站店）</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>7天优品酒店(天津北辰柴楼地铁站店)</t>
+          <t>维也纳3好酒店(天津北辰双街柴楼地铁站店)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2189,11 +2189,11 @@
         <v>105</v>
       </c>
       <c r="I19" t="n">
-        <v>8</v>
+        <v>-5</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>稳房源,提质量</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -2209,13 +2209,13 @@
         <v>30</v>
       </c>
       <c r="O19" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="P19" t="n">
         <v>30</v>
       </c>
       <c r="Q19" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="R19" t="n">
         <v>30</v>
@@ -2255,17 +2255,17 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>6684817408277891079</t>
+          <t>7232169595811924026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>维也纳3好酒店（天津北辰双街柴楼地铁站店）</t>
+          <t>维也纳酒店（天津北辰区华北集团地铁站店）</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>维也纳3好酒店(天津北辰双街柴楼地铁站店)</t>
+          <t>维也纳酒店(天津北辰区华北集团地铁站店)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2277,7 +2277,7 @@
         <v>105</v>
       </c>
       <c r="I20" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -2343,33 +2343,33 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>7232169595811924026</t>
+          <t>7487536797837166592</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>维也纳酒店（天津北辰区华北集团地铁站店）</t>
+          <t>7天优品酒店（天津北辰双街工业园区柴楼地铁站店）</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>维也纳酒店(天津北辰区华北集团地铁站店)</t>
+          <t>7天优品酒店(天津北辰柴楼地铁站店)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>稳房源</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -2391,7 +2391,7 @@
         <v>30</v>
       </c>
       <c r="Q21" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="R21" t="n">
         <v>30</v>
